--- a/Configs/source/Datas/__enums__.xlsx
+++ b/Configs/source/Datas/__enums__.xlsx
@@ -4,12 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="12700" firstSheet="2" activeTab="2"/>
+    <workbookView windowWidth="29100" windowHeight="12700" firstSheet="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Pokemon" sheetId="1" r:id="rId1"/>
-    <sheet name="Element" sheetId="2" r:id="rId2"/>
-    <sheet name="GameMap" sheetId="3" r:id="rId3"/>
+    <sheet name="Card" sheetId="1" r:id="rId1"/>
+    <sheet name="GameMap" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="27">
   <si>
     <t>##var</t>
   </si>
@@ -88,91 +87,19 @@
     <t>注释</t>
   </si>
   <si>
-    <t>PokemonEnum</t>
-  </si>
-  <si>
-    <t>隐潮龙</t>
-  </si>
-  <si>
-    <t>火焰领主</t>
-  </si>
-  <si>
-    <t>推土牛</t>
-  </si>
-  <si>
-    <t>侠客螳螂</t>
-  </si>
-  <si>
-    <t>风绒球</t>
-  </si>
-  <si>
-    <t>毒宝宝</t>
-  </si>
-  <si>
-    <t>一口鲸</t>
-  </si>
-  <si>
-    <t>吞火熊</t>
-  </si>
-  <si>
-    <t>枯木妖</t>
-  </si>
-  <si>
-    <t>斯托姆</t>
-  </si>
-  <si>
-    <t>电电鼠</t>
-  </si>
-  <si>
-    <t>噼啪小将</t>
-  </si>
-  <si>
-    <t>小雀儿</t>
-  </si>
-  <si>
-    <t>布洛克</t>
-  </si>
-  <si>
-    <t>猛毒蝎</t>
-  </si>
-  <si>
-    <t>泡泡海豚</t>
-  </si>
-  <si>
-    <t>火山角羊</t>
-  </si>
-  <si>
-    <t>刺刺猬</t>
-  </si>
-  <si>
-    <t>地蟾蜍</t>
-  </si>
-  <si>
-    <t>ElementEnum</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>火</t>
-  </si>
-  <si>
-    <t>草</t>
-  </si>
-  <si>
-    <t>人造</t>
-  </si>
-  <si>
-    <t>风</t>
-  </si>
-  <si>
-    <t>毒</t>
-  </si>
-  <si>
-    <t>电</t>
-  </si>
-  <si>
-    <t>水</t>
+    <t>CardEnum</t>
+  </si>
+  <si>
+    <t>杀</t>
+  </si>
+  <si>
+    <t>盾</t>
+  </si>
+  <si>
+    <t>桃</t>
+  </si>
+  <si>
+    <t>好桃</t>
   </si>
   <si>
     <t>GameMapEnum</t>
@@ -182,18 +109,6 @@
   </si>
   <si>
     <t>开发测试地图</t>
-  </si>
-  <si>
-    <t>Started</t>
-  </si>
-  <si>
-    <t>序章地图</t>
-  </si>
-  <si>
-    <t>ForsakenCity</t>
-  </si>
-  <si>
-    <t>第一章</t>
   </si>
 </sst>
 </file>
@@ -1314,79 +1229,49 @@
       </c>
     </row>
     <row r="8" spans="8:8">
-      <c r="H8" s="4" t="s">
-        <v>24</v>
-      </c>
+      <c r="H8" s="4"/>
     </row>
     <row r="9" spans="8:8">
-      <c r="H9" s="4" t="s">
-        <v>25</v>
-      </c>
+      <c r="H9" s="4"/>
     </row>
     <row r="10" spans="8:8">
-      <c r="H10" s="4" t="s">
-        <v>26</v>
-      </c>
+      <c r="H10" s="4"/>
     </row>
     <row r="11" spans="8:8">
-      <c r="H11" s="4" t="s">
-        <v>27</v>
-      </c>
+      <c r="H11" s="4"/>
     </row>
     <row r="12" spans="8:8">
-      <c r="H12" s="4" t="s">
-        <v>28</v>
-      </c>
+      <c r="H12" s="4"/>
     </row>
     <row r="13" spans="8:8">
-      <c r="H13" s="4" t="s">
-        <v>29</v>
-      </c>
+      <c r="H13" s="4"/>
     </row>
     <row r="14" spans="8:8">
-      <c r="H14" s="4" t="s">
-        <v>30</v>
-      </c>
+      <c r="H14" s="4"/>
     </row>
     <row r="15" spans="8:8">
-      <c r="H15" s="4" t="s">
-        <v>31</v>
-      </c>
+      <c r="H15" s="4"/>
     </row>
     <row r="16" spans="8:8">
-      <c r="H16" s="4" t="s">
-        <v>32</v>
-      </c>
+      <c r="H16" s="4"/>
     </row>
     <row r="17" spans="8:8">
-      <c r="H17" s="4" t="s">
-        <v>33</v>
-      </c>
+      <c r="H17" s="4"/>
     </row>
     <row r="18" spans="8:8">
-      <c r="H18" s="4" t="s">
-        <v>34</v>
-      </c>
+      <c r="H18" s="4"/>
     </row>
     <row r="19" spans="8:8">
-      <c r="H19" s="4" t="s">
-        <v>35</v>
-      </c>
+      <c r="H19" s="4"/>
     </row>
     <row r="20" spans="8:8">
-      <c r="H20" s="4" t="s">
-        <v>36</v>
-      </c>
+      <c r="H20" s="4"/>
     </row>
     <row r="21" spans="8:8">
-      <c r="H21" s="4" t="s">
-        <v>37</v>
-      </c>
+      <c r="H21" s="4"/>
     </row>
     <row r="22" spans="8:8">
-      <c r="H22" s="4" t="s">
-        <v>38</v>
-      </c>
+      <c r="H22" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1401,159 +1286,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8"/>
-  <cols>
-    <col min="2" max="2" width="19.0357142857143" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" ht="219" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="2:9">
-      <c r="B4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="8:8">
-      <c r="H5" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="8:8">
-      <c r="H6" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="8:8">
-      <c r="H7" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="8:8">
-      <c r="H8" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="8:8">
-      <c r="H9" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="8:8">
-      <c r="H10" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="8:8">
-      <c r="H11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H1:L1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:L23"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8"/>
   <cols>
@@ -1650,50 +1382,23 @@
     </row>
     <row r="4" spans="2:11">
       <c r="B4" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="J4">
         <v>-1</v>
       </c>
       <c r="K4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="8:10">
-      <c r="H5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="8:11">
-      <c r="H6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="8:11">
-      <c r="H7" t="s">
-        <v>53</v>
-      </c>
-      <c r="J7">
-        <v>2</v>
-      </c>
-      <c r="K7" t="s">
-        <v>54</v>
-      </c>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="8:8">
+      <c r="H6" s="4"/>
     </row>
     <row r="8" spans="8:11">
       <c r="H8" s="4"/>

--- a/Configs/source/Datas/__enums__.xlsx
+++ b/Configs/source/Datas/__enums__.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="12700" firstSheet="2"/>
+    <workbookView windowWidth="29100" windowHeight="12700" firstSheet="2" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
-    <sheet name="GameMap" sheetId="3" r:id="rId2"/>
+    <sheet name="Ghost" sheetId="4" r:id="rId2"/>
+    <sheet name="GameMap" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -100,6 +101,15 @@
   </si>
   <si>
     <t>好桃</t>
+  </si>
+  <si>
+    <t>GhostEnum</t>
+  </si>
+  <si>
+    <t>水鬼</t>
+  </si>
+  <si>
+    <t>拔舌鬼</t>
   </si>
   <si>
     <t>GameMapEnum</t>
@@ -1286,6 +1296,129 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" ht="219" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="8:8">
+      <c r="H5" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="8:8">
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="8:8">
+      <c r="H7" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L23"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8"/>
   <cols>
@@ -1382,19 +1515,19 @@
     </row>
     <row r="4" spans="2:11">
       <c r="B4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J4">
         <v>-1</v>
       </c>
       <c r="K4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="8:8">

--- a/Configs/source/Datas/__enums__.xlsx
+++ b/Configs/source/Datas/__enums__.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="12700" firstSheet="2" activeTab="1"/>
+    <workbookView windowWidth="29100" windowHeight="12700" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
     <sheet name="Ghost" sheetId="4" r:id="rId2"/>
-    <sheet name="GameMap" sheetId="3" r:id="rId3"/>
+    <sheet name="Intent" sheetId="5" r:id="rId3"/>
+    <sheet name="GameMap" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -110,6 +111,21 @@
   </si>
   <si>
     <t>拔舌鬼</t>
+  </si>
+  <si>
+    <t>IntentEnum</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>防御</t>
+  </si>
+  <si>
+    <t>喝咖啡</t>
+  </si>
+  <si>
+    <t>吸血</t>
   </si>
   <si>
     <t>GameMapEnum</t>
@@ -1419,6 +1435,133 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" ht="219" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="8:8">
+      <c r="H5" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="8:8">
+      <c r="H6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="8:8">
+      <c r="H7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L23"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8"/>
   <cols>
@@ -1515,19 +1658,19 @@
     </row>
     <row r="4" spans="2:11">
       <c r="B4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J4">
         <v>-1</v>
       </c>
       <c r="K4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="8:8">

--- a/Configs/source/Datas/__enums__.xlsx
+++ b/Configs/source/Datas/__enums__.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="12700" firstSheet="2" activeTab="2"/>
+    <workbookView windowWidth="29100" windowHeight="12700" firstSheet="2" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
     <sheet name="Ghost" sheetId="4" r:id="rId2"/>
     <sheet name="Intent" sheetId="5" r:id="rId3"/>
     <sheet name="GameMap" sheetId="3" r:id="rId4"/>
+    <sheet name="GameLevel" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="40">
   <si>
     <t>##var</t>
   </si>
@@ -135,6 +136,21 @@
   </si>
   <si>
     <t>开发测试地图</t>
+  </si>
+  <si>
+    <t>GameLevel</t>
+  </si>
+  <si>
+    <t>第一关</t>
+  </si>
+  <si>
+    <t>第二关</t>
+  </si>
+  <si>
+    <t>第三关</t>
+  </si>
+  <si>
+    <t>第四关</t>
   </si>
 </sst>
 </file>
@@ -1747,4 +1763,134 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" ht="219" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="2:10">
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="8:8">
+      <c r="H5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="8:8">
+      <c r="H6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="8:8">
+      <c r="H7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Configs/source/Datas/__enums__.xlsx
+++ b/Configs/source/Datas/__enums__.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="41">
   <si>
     <t>##var</t>
   </si>
@@ -138,7 +138,10 @@
     <t>开发测试地图</t>
   </si>
   <si>
-    <t>GameLevel</t>
+    <t>GameLevelEnum</t>
+  </si>
+  <si>
+    <t>None</t>
   </si>
   <si>
     <t>第一关</t>
@@ -1768,8 +1771,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="7"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -1864,7 +1867,7 @@
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" t="s">
         <v>36</v>
       </c>
       <c r="J4">
@@ -1872,7 +1875,7 @@
       </c>
     </row>
     <row r="5" spans="8:8">
-      <c r="H5" t="s">
+      <c r="H5" s="4" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1884,6 +1887,11 @@
     <row r="7" spans="8:8">
       <c r="H7" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="8:8">
+      <c r="H8" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/source/Datas/__enums__.xlsx
+++ b/Configs/source/Datas/__enums__.xlsx
@@ -1,17 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="12700" firstSheet="2" activeTab="4"/>
+    <workbookView windowWidth="25600" windowHeight="12080" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
-    <sheet name="Ghost" sheetId="4" r:id="rId2"/>
-    <sheet name="Intent" sheetId="5" r:id="rId3"/>
-    <sheet name="GameMap" sheetId="3" r:id="rId4"/>
-    <sheet name="GameLevel" sheetId="6" r:id="rId5"/>
+    <sheet name="CardType" sheetId="7" r:id="rId2"/>
+    <sheet name="Ghost" sheetId="4" r:id="rId3"/>
+    <sheet name="Intent" sheetId="5" r:id="rId4"/>
+    <sheet name="GameMap" sheetId="3" r:id="rId5"/>
+    <sheet name="GameLevel" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="80">
   <si>
     <t>##var</t>
   </si>
@@ -93,16 +94,121 @@
     <t>CardEnum</t>
   </si>
   <si>
-    <t>杀</t>
-  </si>
-  <si>
-    <t>盾</t>
-  </si>
-  <si>
-    <t>桃</t>
-  </si>
-  <si>
-    <t>好桃</t>
+    <t>轻击</t>
+  </si>
+  <si>
+    <t>震慑</t>
+  </si>
+  <si>
+    <t>万我</t>
+  </si>
+  <si>
+    <t>吸魂</t>
+  </si>
+  <si>
+    <t>炼魂</t>
+  </si>
+  <si>
+    <t>慷慨</t>
+  </si>
+  <si>
+    <t>静心</t>
+  </si>
+  <si>
+    <t>养神</t>
+  </si>
+  <si>
+    <t>自力更生</t>
+  </si>
+  <si>
+    <t>碎魂</t>
+  </si>
+  <si>
+    <t>壮魂</t>
+  </si>
+  <si>
+    <t>傩戏开场</t>
+  </si>
+  <si>
+    <t>阎王轻击</t>
+  </si>
+  <si>
+    <t>阎王震慑</t>
+  </si>
+  <si>
+    <t>阎王万我</t>
+  </si>
+  <si>
+    <t>阎王吸魂</t>
+  </si>
+  <si>
+    <t>阎王炼魂</t>
+  </si>
+  <si>
+    <t>阎王慷慨</t>
+  </si>
+  <si>
+    <t>阎王静心</t>
+  </si>
+  <si>
+    <t>阎王碎魂</t>
+  </si>
+  <si>
+    <t>面具傩戏</t>
+  </si>
+  <si>
+    <t>无常轻击</t>
+  </si>
+  <si>
+    <t>无常震慑</t>
+  </si>
+  <si>
+    <t>无常万我</t>
+  </si>
+  <si>
+    <t>无常吸魂</t>
+  </si>
+  <si>
+    <t>无常自力</t>
+  </si>
+  <si>
+    <t>阎罗震慑</t>
+  </si>
+  <si>
+    <t>阎罗吸魂</t>
+  </si>
+  <si>
+    <t>阎罗傩戏</t>
+  </si>
+  <si>
+    <t>孟婆熬药攻击</t>
+  </si>
+  <si>
+    <t>孟婆熬药功能</t>
+  </si>
+  <si>
+    <t>孟婆熬药请神</t>
+  </si>
+  <si>
+    <t>二郎神攻击</t>
+  </si>
+  <si>
+    <t>二郎神请神</t>
+  </si>
+  <si>
+    <t>CardTypeEnum</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>功能</t>
+  </si>
+  <si>
+    <t>请神</t>
+  </si>
+  <si>
+    <t>面具</t>
   </si>
   <si>
     <t>GhostEnum</t>
@@ -117,9 +223,6 @@
     <t>IntentEnum</t>
   </si>
   <si>
-    <t>攻击</t>
-  </si>
-  <si>
     <t>防御</t>
   </si>
   <si>
@@ -154,6 +257,21 @@
   </si>
   <si>
     <t>第四关</t>
+  </si>
+  <si>
+    <t>第五关</t>
+  </si>
+  <si>
+    <t>第六关</t>
+  </si>
+  <si>
+    <t>第七关</t>
+  </si>
+  <si>
+    <t>第八关</t>
+  </si>
+  <si>
+    <t>第九关</t>
   </si>
 </sst>
 </file>
@@ -166,7 +284,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,6 +295,13 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -682,150 +807,156 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1147,8 +1278,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:L37"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="20.875" customWidth="1"/>
@@ -1183,13 +1314,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1224,7 +1355,7 @@
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1247,76 +1378,181 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="1:12">
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="8:8">
-      <c r="H5" s="4" t="s">
+    <row r="5" spans="1:12">
+      <c r="H5" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="8:8">
-      <c r="H6" s="4" t="s">
+    <row r="6" spans="1:12">
+      <c r="H6" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="8:8">
-      <c r="H7" s="4" t="s">
+    <row r="7" spans="1:12">
+      <c r="H7" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="8:8">
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="8:8">
-      <c r="H9" s="4"/>
-    </row>
-    <row r="10" spans="8:8">
-      <c r="H10" s="4"/>
-    </row>
-    <row r="11" spans="8:8">
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="8:8">
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" spans="8:8">
-      <c r="H13" s="4"/>
-    </row>
-    <row r="14" spans="8:8">
-      <c r="H14" s="4"/>
-    </row>
-    <row r="15" spans="8:8">
-      <c r="H15" s="4"/>
-    </row>
-    <row r="16" spans="8:8">
-      <c r="H16" s="4"/>
+    <row r="8" spans="1:12">
+      <c r="H8" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="H9" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="H10" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="H11" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="H12" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="H13" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="H14" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="H15" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="H16" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="17" spans="8:8">
-      <c r="H17" s="4"/>
+      <c r="H17" s="4" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="18" spans="8:8">
-      <c r="H18" s="4"/>
+      <c r="H18" s="4" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="19" spans="8:8">
-      <c r="H19" s="4"/>
+      <c r="H19" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="20" spans="8:8">
-      <c r="H20" s="4"/>
+      <c r="H20" s="4" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="21" spans="8:8">
-      <c r="H21" s="4"/>
+      <c r="H21" s="4" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="22" spans="8:8">
-      <c r="H22" s="4"/>
+      <c r="H22" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="8:8">
+      <c r="H23" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="8:8">
+      <c r="H24" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="8:8">
+      <c r="H25" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="8:8">
+      <c r="H26" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="8:8">
+      <c r="H27" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="8:8">
+      <c r="H28" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="8:8">
+      <c r="H29" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="8:8">
+      <c r="H30" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="8:8">
+      <c r="H31" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="8:8">
+      <c r="H32" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="8:8">
+      <c r="H33" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="8:8">
+      <c r="H34" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="8:8">
+      <c r="H35" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" spans="8:8">
+      <c r="H36" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="8:8">
+      <c r="H37" s="6" t="s">
+        <v>53</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1331,8 +1567,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <dimension ref="A1:L22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <cols>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="20.875" customWidth="1"/>
+    <col min="4" max="5" width="14.125" customWidth="1"/>
+    <col min="6" max="6" width="9.375" customWidth="1"/>
+    <col min="7" max="7" width="5" customWidth="1"/>
+    <col min="8" max="8" width="13.5" customWidth="1"/>
+    <col min="9" max="9" width="5.25" customWidth="1"/>
+    <col min="10" max="10" width="12.125" customWidth="1"/>
+    <col min="11" max="11" width="15.125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -1356,13 +1603,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1390,14 +1637,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="99" customHeight="1" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1420,27 +1667,76 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" customFormat="1" spans="1:12">
       <c r="B4" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="8:8">
-      <c r="H5" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="8:8">
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="8:8">
-      <c r="H7" s="4"/>
+      <c r="H4" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:12">
+      <c r="H5" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="1:12">
+      <c r="H6" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:12">
+      <c r="H7" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="1:12">
+      <c r="H8" s="5"/>
+    </row>
+    <row r="9" customFormat="1" spans="1:12">
+      <c r="H9" s="5"/>
+    </row>
+    <row r="10" customFormat="1" spans="1:12">
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" customFormat="1" spans="1:12">
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" customFormat="1" spans="1:12">
+      <c r="H12" s="5"/>
+    </row>
+    <row r="13" customFormat="1" spans="1:12">
+      <c r="H13" s="5"/>
+    </row>
+    <row r="14" customFormat="1" spans="1:12">
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" customFormat="1" spans="1:12">
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" customFormat="1" spans="1:12">
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" customFormat="1" spans="8:8">
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18" customFormat="1" spans="8:8">
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19" customFormat="1" spans="8:8">
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" customFormat="1" spans="8:8">
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" customFormat="1" spans="8:8">
+      <c r="H21" s="4"/>
+    </row>
+    <row r="22" customFormat="1" spans="8:8">
+      <c r="H22" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1455,7 +1751,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14" outlineLevelRow="6"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -1479,13 +1775,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1513,14 +1809,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="168" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1543,31 +1839,27 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="1:12">
       <c r="B4" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="8:8">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="H5" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="8:8">
-      <c r="H6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="8:8">
-      <c r="H7" t="s">
-        <v>31</v>
-      </c>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="H7" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1581,13 +1873,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L23"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8"/>
-  <cols>
-    <col min="2" max="2" width="14.875" customWidth="1"/>
-    <col min="10" max="10" width="12.1964285714286" customWidth="1"/>
-    <col min="11" max="11" width="16.0714285714286" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14" outlineLevelRow="6"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -1611,13 +1898,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1645,14 +1932,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="168" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1675,89 +1962,31 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:11">
+    <row r="4" spans="1:12">
       <c r="B4" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4">
-        <v>-1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="8:8">
-      <c r="H6" s="4"/>
-    </row>
-    <row r="8" spans="8:11">
-      <c r="H8" s="4"/>
-      <c r="K8" s="4"/>
-    </row>
-    <row r="9" spans="8:11">
-      <c r="H9" s="4"/>
-      <c r="K9" s="4"/>
-    </row>
-    <row r="10" spans="8:11">
-      <c r="H10" s="4"/>
-      <c r="K10" s="4"/>
-    </row>
-    <row r="11" spans="8:11">
-      <c r="H11" s="4"/>
-      <c r="K11" s="4"/>
-    </row>
-    <row r="12" spans="8:11">
-      <c r="H12" s="4"/>
-      <c r="K12" s="4"/>
-    </row>
-    <row r="13" spans="8:11">
-      <c r="H13" s="4"/>
-      <c r="K13" s="4"/>
-    </row>
-    <row r="14" spans="8:11">
-      <c r="H14" s="4"/>
-      <c r="K14" s="4"/>
-    </row>
-    <row r="15" spans="8:11">
-      <c r="H15" s="4"/>
-      <c r="K15" s="4"/>
-    </row>
-    <row r="16" spans="8:11">
-      <c r="H16" s="4"/>
-      <c r="K16" s="4"/>
-    </row>
-    <row r="17" spans="8:11">
-      <c r="H17" s="4"/>
-      <c r="K17" s="4"/>
-    </row>
-    <row r="18" spans="8:11">
-      <c r="H18" s="4"/>
-      <c r="K18" s="4"/>
-    </row>
-    <row r="19" spans="8:11">
-      <c r="H19" s="4"/>
-      <c r="K19" s="4"/>
-    </row>
-    <row r="20" spans="8:11">
-      <c r="H20" s="4"/>
-      <c r="K20" s="4"/>
-    </row>
-    <row r="21" spans="8:11">
-      <c r="H21" s="4"/>
-      <c r="K21" s="4"/>
-    </row>
-    <row r="22" spans="8:11">
-      <c r="H22" s="4"/>
-      <c r="K22" s="4"/>
-    </row>
-    <row r="23" spans="8:11">
-      <c r="H23" s="4"/>
-      <c r="K23" s="4"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="H5" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="H6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="H7" t="s">
+        <v>65</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1771,8 +2000,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="7"/>
+  <dimension ref="A1:L23"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14"/>
+  <cols>
+    <col min="2" max="2" width="14.875" customWidth="1"/>
+    <col min="10" max="10" width="12.2" customWidth="1"/>
+    <col min="11" max="11" width="16.075" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -1796,13 +2030,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1830,14 +2064,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="168" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1860,38 +2094,248 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="1:12">
       <c r="B4" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
+      <c r="H4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="J4">
+        <v>-1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="H6" s="4"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="H8" s="4"/>
+      <c r="K8" s="4"/>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="H9" s="4"/>
+      <c r="K9" s="4"/>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="H10" s="4"/>
+      <c r="K10" s="4"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="H11" s="4"/>
+      <c r="K11" s="4"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="H12" s="4"/>
+      <c r="K12" s="4"/>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="H13" s="4"/>
+      <c r="K13" s="4"/>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="H14" s="4"/>
+      <c r="K14" s="4"/>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="H15" s="4"/>
+      <c r="K15" s="4"/>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="H16" s="4"/>
+      <c r="K16" s="4"/>
+    </row>
+    <row r="17" spans="8:11">
+      <c r="H17" s="4"/>
+      <c r="K17" s="4"/>
+    </row>
+    <row r="18" spans="8:11">
+      <c r="H18" s="4"/>
+      <c r="K18" s="4"/>
+    </row>
+    <row r="19" spans="8:11">
+      <c r="H19" s="4"/>
+      <c r="K19" s="4"/>
+    </row>
+    <row r="20" spans="8:11">
+      <c r="H20" s="4"/>
+      <c r="K20" s="4"/>
+    </row>
+    <row r="21" spans="8:11">
+      <c r="H21" s="4"/>
+      <c r="K21" s="4"/>
+    </row>
+    <row r="22" spans="8:11">
+      <c r="H22" s="4"/>
+      <c r="K22" s="4"/>
+    </row>
+    <row r="23" spans="8:11">
+      <c r="H23" s="4"/>
+      <c r="K23" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" ht="168" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="8:8">
+    <row r="5" spans="1:12">
       <c r="H5" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="8:8">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="H6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="8:8">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="H7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="8:8">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="H8" t="s">
-        <v>40</v>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="H9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="H10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="H11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="H12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="H13" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/source/Datas/__enums__.xlsx
+++ b/Configs/source/Datas/__enums__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" firstSheet="2"/>
+    <workbookView windowWidth="29100" windowHeight="12700" firstSheet="2" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="Intent" sheetId="5" r:id="rId4"/>
     <sheet name="GameMap" sheetId="3" r:id="rId5"/>
     <sheet name="GameLevel" sheetId="6" r:id="rId6"/>
+    <sheet name="Mask" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="87">
   <si>
     <t>##var</t>
   </si>
@@ -272,6 +273,27 @@
   </si>
   <si>
     <t>第九关</t>
+  </si>
+  <si>
+    <t>MaskEnum</t>
+  </si>
+  <si>
+    <t>本我</t>
+  </si>
+  <si>
+    <t>阎王</t>
+  </si>
+  <si>
+    <t>十殿阎罗</t>
+  </si>
+  <si>
+    <t>黑白无常</t>
+  </si>
+  <si>
+    <t>孟婆</t>
+  </si>
+  <si>
+    <t>二郎神</t>
   </si>
 </sst>
 </file>
@@ -945,10 +967,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1279,7 +1301,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="20.875" customWidth="1"/>
@@ -1314,13 +1336,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1355,7 +1377,7 @@
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1378,7 +1400,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="2:8">
       <c r="B4" t="s">
         <v>19</v>
       </c>
@@ -1389,62 +1411,62 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="8:8">
       <c r="H5" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="8:8">
       <c r="H6" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="8:8">
       <c r="H7" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="8:8">
       <c r="H8" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="8:8">
       <c r="H9" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="8:8">
       <c r="H10" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="8:8">
       <c r="H11" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="8:8">
       <c r="H12" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="8:8">
       <c r="H13" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="8:8">
       <c r="H14" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="8:8">
       <c r="H15" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="8:8">
       <c r="H16" s="4" t="s">
         <v>32</v>
       </c>
@@ -1568,7 +1590,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="20.875" customWidth="1"/>
@@ -1603,13 +1625,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1644,7 +1666,7 @@
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1667,7 +1689,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" customFormat="1" spans="1:12">
+    <row r="4" customFormat="1" spans="2:8">
       <c r="B4" t="s">
         <v>54</v>
       </c>
@@ -1678,46 +1700,46 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:12">
+    <row r="5" customFormat="1" spans="8:8">
       <c r="H5" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="1:12">
+    <row r="6" customFormat="1" spans="8:8">
       <c r="H6" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="1:12">
+    <row r="7" customFormat="1" spans="8:8">
       <c r="H7" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="8" customFormat="1" spans="1:12">
+    <row r="8" customFormat="1" spans="8:8">
       <c r="H8" s="5"/>
     </row>
-    <row r="9" customFormat="1" spans="1:12">
+    <row r="9" customFormat="1" spans="8:8">
       <c r="H9" s="5"/>
     </row>
-    <row r="10" customFormat="1" spans="1:12">
+    <row r="10" customFormat="1" spans="8:8">
       <c r="H10" s="5"/>
     </row>
-    <row r="11" customFormat="1" spans="1:12">
+    <row r="11" customFormat="1" spans="8:8">
       <c r="H11" s="5"/>
     </row>
-    <row r="12" customFormat="1" spans="1:12">
+    <row r="12" customFormat="1" spans="8:8">
       <c r="H12" s="5"/>
     </row>
-    <row r="13" customFormat="1" spans="1:12">
+    <row r="13" customFormat="1" spans="8:8">
       <c r="H13" s="5"/>
     </row>
-    <row r="14" customFormat="1" spans="1:12">
+    <row r="14" customFormat="1" spans="8:8">
       <c r="H14" s="5"/>
     </row>
-    <row r="15" customFormat="1" spans="1:12">
+    <row r="15" customFormat="1" spans="8:8">
       <c r="H15" s="5"/>
     </row>
-    <row r="16" customFormat="1" spans="1:12">
+    <row r="16" customFormat="1" spans="8:8">
       <c r="H16" s="4"/>
     </row>
     <row r="17" customFormat="1" spans="8:8">
@@ -1751,7 +1773,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -1775,13 +1797,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1809,14 +1831,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="168" spans="1:12">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1839,7 +1861,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="2:8">
       <c r="B4" t="s">
         <v>59</v>
       </c>
@@ -1850,15 +1872,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="8:8">
       <c r="H5" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="8:8">
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="8:8">
       <c r="H7" s="4"/>
     </row>
   </sheetData>
@@ -1874,7 +1896,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -1898,13 +1920,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1932,14 +1954,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="168" spans="1:12">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1962,7 +1984,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="2:8">
       <c r="B4" t="s">
         <v>62</v>
       </c>
@@ -1973,17 +1995,17 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="8:8">
       <c r="H5" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="8:8">
       <c r="H6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="8:8">
       <c r="H7" t="s">
         <v>65</v>
       </c>
@@ -2001,11 +2023,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L23"/>
-  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="14.875" customWidth="1"/>
-    <col min="10" max="10" width="12.2" customWidth="1"/>
-    <col min="11" max="11" width="16.075" customWidth="1"/>
+    <col min="10" max="10" width="12.1964285714286" customWidth="1"/>
+    <col min="11" max="11" width="16.0714285714286" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -2030,13 +2052,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -2064,14 +2086,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="168" spans="1:12">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2094,7 +2116,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="2:11">
       <c r="B4" t="s">
         <v>66</v>
       </c>
@@ -2111,42 +2133,42 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="8:8">
       <c r="H6" s="4"/>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="8:11">
       <c r="H8" s="4"/>
       <c r="K8" s="4"/>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="8:11">
       <c r="H9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="8:11">
       <c r="H10" s="4"/>
       <c r="K10" s="4"/>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="8:11">
       <c r="H11" s="4"/>
       <c r="K11" s="4"/>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="8:11">
       <c r="H12" s="4"/>
       <c r="K12" s="4"/>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="8:11">
       <c r="H13" s="4"/>
       <c r="K13" s="4"/>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="8:11">
       <c r="H14" s="4"/>
       <c r="K14" s="4"/>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="8:11">
       <c r="H15" s="4"/>
       <c r="K15" s="4"/>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="8:11">
       <c r="H16" s="4"/>
       <c r="K16" s="4"/>
     </row>
@@ -2191,7 +2213,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -2215,13 +2237,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -2249,14 +2271,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="168" spans="1:12">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2279,7 +2301,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
         <v>69</v>
       </c>
@@ -2293,49 +2315,189 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="8:8">
       <c r="H5" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="8:8">
       <c r="H6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="8:8">
       <c r="H7" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="8:8">
       <c r="H8" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="8:8">
       <c r="H9" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="8:8">
       <c r="H10" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="8:8">
       <c r="H11" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="8:8">
       <c r="H12" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="8:8">
       <c r="H13" t="s">
         <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8"/>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" ht="219" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="2:10">
+      <c r="B4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="8:8">
+      <c r="H5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="8:8">
+      <c r="H6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="8:8">
+      <c r="H7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="8:8">
+      <c r="H8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="8:8">
+      <c r="H9" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/source/Datas/__enums__.xlsx
+++ b/Configs/source/Datas/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="12700" firstSheet="2" activeTab="6"/>
+    <workbookView windowWidth="29100" windowHeight="12700" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="88">
   <si>
     <t>##var</t>
   </si>
@@ -195,6 +195,9 @@
   </si>
   <si>
     <t>二郎神请神</t>
+  </si>
+  <si>
+    <t>结束回合</t>
   </si>
   <si>
     <t>CardTypeEnum</t>
@@ -1300,7 +1303,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -1574,6 +1577,11 @@
     <row r="37" spans="8:8">
       <c r="H37" s="6" t="s">
         <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="8:8">
+      <c r="H38" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1691,28 +1699,28 @@
     </row>
     <row r="4" customFormat="1" spans="2:8">
       <c r="B4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="8:8">
       <c r="H5" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" customFormat="1" spans="8:8">
       <c r="H6" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="8:8">
       <c r="H7" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="8:8">
@@ -1863,18 +1871,18 @@
     </row>
     <row r="4" spans="2:8">
       <c r="B4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="8:8">
       <c r="H5" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="8:8">
@@ -1986,28 +1994,28 @@
     </row>
     <row r="4" spans="2:8">
       <c r="B4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="8:8">
       <c r="H5" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="8:8">
       <c r="H6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="8:8">
       <c r="H7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -2118,19 +2126,19 @@
     </row>
     <row r="4" spans="2:11">
       <c r="B4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J4">
         <v>-1</v>
       </c>
       <c r="K4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="8:8">
@@ -2303,13 +2311,13 @@
     </row>
     <row r="4" spans="2:10">
       <c r="B4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2317,47 +2325,47 @@
     </row>
     <row r="5" spans="8:8">
       <c r="H5" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="8:8">
       <c r="H6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="8:8">
       <c r="H7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="8:8">
       <c r="H8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="8:8">
       <c r="H9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="8:8">
       <c r="H10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="8:8">
       <c r="H11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="8:8">
       <c r="H12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="8:8">
       <c r="H13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2463,13 +2471,13 @@
     </row>
     <row r="4" spans="2:10">
       <c r="B4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2477,27 +2485,27 @@
     </row>
     <row r="5" spans="8:8">
       <c r="H5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="8:8">
       <c r="H6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="8:8">
       <c r="H7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="8:8">
       <c r="H8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="8:8">
       <c r="H9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/source/Datas/__enums__.xlsx
+++ b/Configs/source/Datas/__enums__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="12700" firstSheet="2"/>
+    <workbookView windowWidth="25600" windowHeight="12080" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="101">
   <si>
     <t>##var</t>
   </si>
@@ -95,6 +95,9 @@
     <t>CardEnum</t>
   </si>
   <si>
+    <t>None</t>
+  </si>
+  <si>
     <t>轻击</t>
   </si>
   <si>
@@ -200,6 +203,45 @@
     <t>结束回合</t>
   </si>
   <si>
+    <t>拔舌鬼攻击</t>
+  </si>
+  <si>
+    <t>穷鬼吸血</t>
+  </si>
+  <si>
+    <t>铜柱鬼叠甲</t>
+  </si>
+  <si>
+    <t>铜柱鬼攻击</t>
+  </si>
+  <si>
+    <t>肉山鬼攻击</t>
+  </si>
+  <si>
+    <t>水鬼攻击</t>
+  </si>
+  <si>
+    <t>阎王攻击</t>
+  </si>
+  <si>
+    <t>阎王空过</t>
+  </si>
+  <si>
+    <t>阎王叠甲</t>
+  </si>
+  <si>
+    <t>阎王减少死期</t>
+  </si>
+  <si>
+    <t>黑白无常攻击</t>
+  </si>
+  <si>
+    <t>黑白无常打自己</t>
+  </si>
+  <si>
+    <t>黑白无常叠甲</t>
+  </si>
+  <si>
     <t>CardTypeEnum</t>
   </si>
   <si>
@@ -246,9 +288,6 @@
   </si>
   <si>
     <t>GameLevelEnum</t>
-  </si>
-  <si>
-    <t>None</t>
   </si>
   <si>
     <t>第一关</t>
@@ -970,10 +1009,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1303,8 +1342,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:L52"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="20.875" customWidth="1"/>
@@ -1339,13 +1378,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1380,7 +1419,7 @@
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1403,74 +1442,77 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="1:12">
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="8:8">
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="H5" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="8:8">
+    <row r="6" spans="1:12">
       <c r="H6" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="8:8">
+    <row r="7" spans="1:12">
       <c r="H7" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="8:8">
+    <row r="8" spans="1:12">
       <c r="H8" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="8:8">
+    <row r="9" spans="1:12">
       <c r="H9" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="8:8">
+    <row r="10" spans="1:12">
       <c r="H10" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="8:8">
+    <row r="11" spans="1:12">
       <c r="H11" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="8:8">
+    <row r="12" spans="1:12">
       <c r="H12" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="8:8">
+    <row r="13" spans="1:12">
       <c r="H13" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="8:8">
+    <row r="14" spans="1:12">
       <c r="H14" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="8:8">
+    <row r="15" spans="1:12">
       <c r="H15" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="8:8">
-      <c r="H16" s="4" t="s">
+    <row r="16" spans="1:12">
+      <c r="H16" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1505,7 +1547,7 @@
       </c>
     </row>
     <row r="23" spans="8:8">
-      <c r="H23" s="6" t="s">
+      <c r="H23" s="4" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1580,8 +1622,78 @@
       </c>
     </row>
     <row r="38" spans="8:8">
-      <c r="H38" t="s">
+      <c r="H38" s="6" t="s">
         <v>54</v>
+      </c>
+    </row>
+    <row r="39" spans="8:8">
+      <c r="H39" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="8:8">
+      <c r="H40" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" spans="8:8">
+      <c r="H41" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="42" spans="8:8">
+      <c r="H42" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="8:8">
+      <c r="H43" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="44" spans="8:8">
+      <c r="H44" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="8:8">
+      <c r="H45" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="8:8">
+      <c r="H46" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="47" spans="8:8">
+      <c r="H47" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="48" spans="8:8">
+      <c r="H48" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="49" spans="8:8">
+      <c r="H49" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="50" spans="8:8">
+      <c r="H50" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="51" spans="8:8">
+      <c r="H51" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="52" spans="8:8">
+      <c r="H52" s="6" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1598,7 +1710,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="20.875" customWidth="1"/>
@@ -1633,13 +1745,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1674,7 +1786,7 @@
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1697,57 +1809,57 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" customFormat="1" spans="2:8">
+    <row r="4" customFormat="1" spans="1:12">
       <c r="B4" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" customFormat="1" spans="8:8">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:12">
       <c r="H5" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" spans="8:8">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="1:12">
       <c r="H6" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" customFormat="1" spans="8:8">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:12">
       <c r="H7" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" customFormat="1" spans="8:8">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="1:12">
       <c r="H8" s="5"/>
     </row>
-    <row r="9" customFormat="1" spans="8:8">
+    <row r="9" customFormat="1" spans="1:12">
       <c r="H9" s="5"/>
     </row>
-    <row r="10" customFormat="1" spans="8:8">
+    <row r="10" customFormat="1" spans="1:12">
       <c r="H10" s="5"/>
     </row>
-    <row r="11" customFormat="1" spans="8:8">
+    <row r="11" customFormat="1" spans="1:12">
       <c r="H11" s="5"/>
     </row>
-    <row r="12" customFormat="1" spans="8:8">
+    <row r="12" customFormat="1" spans="1:12">
       <c r="H12" s="5"/>
     </row>
-    <row r="13" customFormat="1" spans="8:8">
+    <row r="13" customFormat="1" spans="1:12">
       <c r="H13" s="5"/>
     </row>
-    <row r="14" customFormat="1" spans="8:8">
+    <row r="14" customFormat="1" spans="1:12">
       <c r="H14" s="5"/>
     </row>
-    <row r="15" customFormat="1" spans="8:8">
+    <row r="15" customFormat="1" spans="1:12">
       <c r="H15" s="5"/>
     </row>
-    <row r="16" customFormat="1" spans="8:8">
+    <row r="16" customFormat="1" spans="1:12">
       <c r="H16" s="4"/>
     </row>
     <row r="17" customFormat="1" spans="8:8">
@@ -1781,7 +1893,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14" outlineLevelRow="6"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -1805,13 +1917,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1839,14 +1951,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="168" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1869,26 +1981,26 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="1:12">
       <c r="B4" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="8:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="H5" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="8:8">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="8:8">
+    <row r="7" spans="1:12">
       <c r="H7" s="4"/>
     </row>
   </sheetData>
@@ -1904,7 +2016,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14" outlineLevelRow="6"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -1928,13 +2040,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1962,14 +2074,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="168" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1992,30 +2104,30 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="1:12">
       <c r="B4" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="8:8">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="H5" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="8:8">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="H6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="8:8">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="H7" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2031,11 +2143,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L23"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="14.875" customWidth="1"/>
-    <col min="10" max="10" width="12.1964285714286" customWidth="1"/>
-    <col min="11" max="11" width="16.0714285714286" customWidth="1"/>
+    <col min="10" max="10" width="12.2" customWidth="1"/>
+    <col min="11" max="11" width="16.075" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -2060,13 +2172,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -2094,14 +2206,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="168" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2124,59 +2236,59 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:11">
+    <row r="4" spans="1:12">
       <c r="B4" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="J4">
         <v>-1</v>
       </c>
       <c r="K4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="8:8">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="H6" s="4"/>
     </row>
-    <row r="8" spans="8:11">
+    <row r="8" spans="1:12">
       <c r="H8" s="4"/>
       <c r="K8" s="4"/>
     </row>
-    <row r="9" spans="8:11">
+    <row r="9" spans="1:12">
       <c r="H9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" spans="8:11">
+    <row r="10" spans="1:12">
       <c r="H10" s="4"/>
       <c r="K10" s="4"/>
     </row>
-    <row r="11" spans="8:11">
+    <row r="11" spans="1:12">
       <c r="H11" s="4"/>
       <c r="K11" s="4"/>
     </row>
-    <row r="12" spans="8:11">
+    <row r="12" spans="1:12">
       <c r="H12" s="4"/>
       <c r="K12" s="4"/>
     </row>
-    <row r="13" spans="8:11">
+    <row r="13" spans="1:12">
       <c r="H13" s="4"/>
       <c r="K13" s="4"/>
     </row>
-    <row r="14" spans="8:11">
+    <row r="14" spans="1:12">
       <c r="H14" s="4"/>
       <c r="K14" s="4"/>
     </row>
-    <row r="15" spans="8:11">
+    <row r="15" spans="1:12">
       <c r="H15" s="4"/>
       <c r="K15" s="4"/>
     </row>
-    <row r="16" spans="8:11">
+    <row r="16" spans="1:12">
       <c r="H16" s="4"/>
       <c r="K16" s="4"/>
     </row>
@@ -2221,7 +2333,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -2245,13 +2357,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -2279,14 +2391,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="168" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2309,63 +2421,63 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="1:12">
       <c r="B4" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="8:8">
+    <row r="5" spans="1:12">
       <c r="H5" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="8:8">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="H6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="8:8">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="H7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="8:8">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="H8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="8:8">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="H9" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="8:8">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="H10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" spans="8:8">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="H11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="12" spans="8:8">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="H12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" spans="8:8">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="H13" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2381,7 +2493,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -2405,13 +2517,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -2439,14 +2551,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="168" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2469,43 +2581,43 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="1:12">
       <c r="B4" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="8:8">
+    <row r="5" spans="1:12">
       <c r="H5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="8:8">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="H6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="8:8">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="H7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8" spans="8:8">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="H8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="8:8">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="H9" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/source/Datas/__enums__.xlsx
+++ b/Configs/source/Datas/__enums__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" firstSheet="2"/>
+    <workbookView windowWidth="29100" windowHeight="12700" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
@@ -233,6 +233,9 @@
     <t>阎王减少死期</t>
   </si>
   <si>
+    <t>阎王施加死期</t>
+  </si>
+  <si>
     <t>黑白无常攻击</t>
   </si>
   <si>
@@ -323,19 +326,16 @@
     <t>本我</t>
   </si>
   <si>
-    <t>阎王</t>
-  </si>
-  <si>
-    <t>十殿阎罗</t>
-  </si>
-  <si>
-    <t>黑白无常</t>
-  </si>
-  <si>
-    <t>孟婆</t>
-  </si>
-  <si>
-    <t>二郎神</t>
+    <t>阎王面具</t>
+  </si>
+  <si>
+    <t>无常面具</t>
+  </si>
+  <si>
+    <t>孟婆面具</t>
+  </si>
+  <si>
+    <t>二郎神面具</t>
   </si>
 </sst>
 </file>
@@ -1009,10 +1009,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1342,8 +1342,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L52"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:L53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="20.875" customWidth="1"/>
@@ -1378,13 +1378,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1419,7 +1419,7 @@
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
         <v>19</v>
       </c>
@@ -1456,62 +1456,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="8:8">
       <c r="H5" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="8:8">
       <c r="H6" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="8:8">
       <c r="H7" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="8:8">
       <c r="H8" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="8:8">
       <c r="H9" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="8:8">
       <c r="H10" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="8:8">
       <c r="H11" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="8:8">
       <c r="H12" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="8:8">
       <c r="H13" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="8:8">
       <c r="H14" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="8:8">
       <c r="H15" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="8:8">
       <c r="H16" s="5" t="s">
         <v>32</v>
       </c>
@@ -1682,7 +1682,7 @@
       </c>
     </row>
     <row r="50" spans="8:8">
-      <c r="H50" s="6" t="s">
+      <c r="H50" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1694,6 +1694,11 @@
     <row r="52" spans="8:8">
       <c r="H52" s="6" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="53" spans="8:8">
+      <c r="H53" s="6" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1710,7 +1715,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="20.875" customWidth="1"/>
@@ -1745,13 +1750,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1786,7 +1791,7 @@
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1809,57 +1814,57 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" customFormat="1" spans="1:12">
+    <row r="4" customFormat="1" spans="2:8">
       <c r="B4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" customFormat="1" spans="1:12">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="8:8">
       <c r="H5" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" spans="1:12">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="8:8">
       <c r="H6" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" customFormat="1" spans="1:12">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="8:8">
       <c r="H7" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="8" customFormat="1" spans="1:12">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="8:8">
       <c r="H8" s="5"/>
     </row>
-    <row r="9" customFormat="1" spans="1:12">
+    <row r="9" customFormat="1" spans="8:8">
       <c r="H9" s="5"/>
     </row>
-    <row r="10" customFormat="1" spans="1:12">
+    <row r="10" customFormat="1" spans="8:8">
       <c r="H10" s="5"/>
     </row>
-    <row r="11" customFormat="1" spans="1:12">
+    <row r="11" customFormat="1" spans="8:8">
       <c r="H11" s="5"/>
     </row>
-    <row r="12" customFormat="1" spans="1:12">
+    <row r="12" customFormat="1" spans="8:8">
       <c r="H12" s="5"/>
     </row>
-    <row r="13" customFormat="1" spans="1:12">
+    <row r="13" customFormat="1" spans="8:8">
       <c r="H13" s="5"/>
     </row>
-    <row r="14" customFormat="1" spans="1:12">
+    <row r="14" customFormat="1" spans="8:8">
       <c r="H14" s="5"/>
     </row>
-    <row r="15" customFormat="1" spans="1:12">
+    <row r="15" customFormat="1" spans="8:8">
       <c r="H15" s="5"/>
     </row>
-    <row r="16" customFormat="1" spans="1:12">
+    <row r="16" customFormat="1" spans="8:8">
       <c r="H16" s="4"/>
     </row>
     <row r="17" customFormat="1" spans="8:8">
@@ -1893,7 +1898,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -1917,13 +1922,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1951,14 +1956,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="168" spans="1:12">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1981,26 +1986,26 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="2:8">
       <c r="B4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="8:8">
       <c r="H5" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="8:8">
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="8:8">
       <c r="H7" s="4"/>
     </row>
   </sheetData>
@@ -2016,7 +2021,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -2040,13 +2045,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -2074,14 +2079,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="168" spans="1:12">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2104,30 +2109,30 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="2:8">
       <c r="B4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="8:8">
       <c r="H5" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="8:8">
       <c r="H6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="8:8">
       <c r="H7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -2143,11 +2148,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L23"/>
-  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="14.875" customWidth="1"/>
-    <col min="10" max="10" width="12.2" customWidth="1"/>
-    <col min="11" max="11" width="16.075" customWidth="1"/>
+    <col min="10" max="10" width="12.1964285714286" customWidth="1"/>
+    <col min="11" max="11" width="16.0714285714286" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -2172,13 +2177,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -2206,14 +2211,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="168" spans="1:12">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2236,59 +2241,59 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="2:11">
       <c r="B4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J4">
         <v>-1</v>
       </c>
       <c r="K4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="8:8">
       <c r="H6" s="4"/>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="8:11">
       <c r="H8" s="4"/>
       <c r="K8" s="4"/>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="8:11">
       <c r="H9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="8:11">
       <c r="H10" s="4"/>
       <c r="K10" s="4"/>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="8:11">
       <c r="H11" s="4"/>
       <c r="K11" s="4"/>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="8:11">
       <c r="H12" s="4"/>
       <c r="K12" s="4"/>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="8:11">
       <c r="H13" s="4"/>
       <c r="K13" s="4"/>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="8:11">
       <c r="H14" s="4"/>
       <c r="K14" s="4"/>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="8:11">
       <c r="H15" s="4"/>
       <c r="K15" s="4"/>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="8:11">
       <c r="H16" s="4"/>
       <c r="K16" s="4"/>
     </row>
@@ -2333,7 +2338,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -2357,13 +2362,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -2391,14 +2396,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="168" spans="1:12">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2421,9 +2426,9 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -2435,49 +2440,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="8:8">
       <c r="H5" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="8:8">
       <c r="H6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="8:8">
       <c r="H7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="8:8">
       <c r="H8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="8:8">
       <c r="H9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="8:8">
       <c r="H10" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="8:8">
       <c r="H11" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="8:8">
       <c r="H12" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="8:8">
       <c r="H13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -2492,8 +2497,8 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14"/>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="7"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -2517,13 +2522,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -2551,14 +2556,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="168" spans="1:12">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2581,42 +2586,37 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="8:8">
       <c r="H5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="8:8">
       <c r="H6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="8:8">
       <c r="H7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="8:8">
       <c r="H8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="H9" t="s">
         <v>100</v>
       </c>
     </row>

--- a/Configs/source/Datas/__enums__.xlsx
+++ b/Configs/source/Datas/__enums__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="12700" firstSheet="2"/>
+    <workbookView windowWidth="25600" windowHeight="12080" firstSheet="2" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="102">
   <si>
     <t>##var</t>
   </si>
@@ -330,6 +330,9 @@
   </si>
   <si>
     <t>无常面具</t>
+  </si>
+  <si>
+    <t>阎罗面具</t>
   </si>
   <si>
     <t>孟婆面具</t>
@@ -1009,10 +1012,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1343,7 +1346,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="20.875" customWidth="1"/>
@@ -1378,13 +1381,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1419,7 +1422,7 @@
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1442,7 +1445,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="1:12">
       <c r="B4" t="s">
         <v>19</v>
       </c>
@@ -1456,62 +1459,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="8:8">
+    <row r="5" spans="1:12">
       <c r="H5" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="8:8">
+    <row r="6" spans="1:12">
       <c r="H6" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="8:8">
+    <row r="7" spans="1:12">
       <c r="H7" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="8:8">
+    <row r="8" spans="1:12">
       <c r="H8" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="8:8">
+    <row r="9" spans="1:12">
       <c r="H9" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="8:8">
+    <row r="10" spans="1:12">
       <c r="H10" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="8:8">
+    <row r="11" spans="1:12">
       <c r="H11" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="8:8">
+    <row r="12" spans="1:12">
       <c r="H12" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="8:8">
+    <row r="13" spans="1:12">
       <c r="H13" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="8:8">
+    <row r="14" spans="1:12">
       <c r="H14" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="8:8">
+    <row r="15" spans="1:12">
       <c r="H15" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="8:8">
+    <row r="16" spans="1:12">
       <c r="H16" s="5" t="s">
         <v>32</v>
       </c>
@@ -1715,7 +1718,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="20.875" customWidth="1"/>
@@ -1750,13 +1753,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1791,7 +1794,7 @@
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1814,7 +1817,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" customFormat="1" spans="2:8">
+    <row r="4" customFormat="1" spans="1:12">
       <c r="B4" t="s">
         <v>70</v>
       </c>
@@ -1825,46 +1828,46 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="8:8">
+    <row r="5" customFormat="1" spans="1:12">
       <c r="H5" s="5" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="8:8">
+    <row r="6" customFormat="1" spans="1:12">
       <c r="H6" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="8:8">
+    <row r="7" customFormat="1" spans="1:12">
       <c r="H7" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="8" customFormat="1" spans="8:8">
+    <row r="8" customFormat="1" spans="1:12">
       <c r="H8" s="5"/>
     </row>
-    <row r="9" customFormat="1" spans="8:8">
+    <row r="9" customFormat="1" spans="1:12">
       <c r="H9" s="5"/>
     </row>
-    <row r="10" customFormat="1" spans="8:8">
+    <row r="10" customFormat="1" spans="1:12">
       <c r="H10" s="5"/>
     </row>
-    <row r="11" customFormat="1" spans="8:8">
+    <row r="11" customFormat="1" spans="1:12">
       <c r="H11" s="5"/>
     </row>
-    <row r="12" customFormat="1" spans="8:8">
+    <row r="12" customFormat="1" spans="1:12">
       <c r="H12" s="5"/>
     </row>
-    <row r="13" customFormat="1" spans="8:8">
+    <row r="13" customFormat="1" spans="1:12">
       <c r="H13" s="5"/>
     </row>
-    <row r="14" customFormat="1" spans="8:8">
+    <row r="14" customFormat="1" spans="1:12">
       <c r="H14" s="5"/>
     </row>
-    <row r="15" customFormat="1" spans="8:8">
+    <row r="15" customFormat="1" spans="1:12">
       <c r="H15" s="5"/>
     </row>
-    <row r="16" customFormat="1" spans="8:8">
+    <row r="16" customFormat="1" spans="1:12">
       <c r="H16" s="4"/>
     </row>
     <row r="17" customFormat="1" spans="8:8">
@@ -1898,7 +1901,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14" outlineLevelRow="6"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -1922,13 +1925,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1956,14 +1959,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="168" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1986,7 +1989,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="1:12">
       <c r="B4" t="s">
         <v>75</v>
       </c>
@@ -1997,15 +2000,15 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="8:8">
+    <row r="5" spans="1:12">
       <c r="H5" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="8:8">
+    <row r="6" spans="1:12">
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="8:8">
+    <row r="7" spans="1:12">
       <c r="H7" s="4"/>
     </row>
   </sheetData>
@@ -2021,7 +2024,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14" outlineLevelRow="6"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -2045,13 +2048,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -2079,14 +2082,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="168" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2109,7 +2112,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="1:12">
       <c r="B4" t="s">
         <v>78</v>
       </c>
@@ -2120,17 +2123,17 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="8:8">
+    <row r="5" spans="1:12">
       <c r="H5" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="8:8">
+    <row r="6" spans="1:12">
       <c r="H6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="8:8">
+    <row r="7" spans="1:12">
       <c r="H7" t="s">
         <v>81</v>
       </c>
@@ -2148,11 +2151,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L23"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="14.875" customWidth="1"/>
-    <col min="10" max="10" width="12.1964285714286" customWidth="1"/>
-    <col min="11" max="11" width="16.0714285714286" customWidth="1"/>
+    <col min="10" max="10" width="12.2" customWidth="1"/>
+    <col min="11" max="11" width="16.075" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -2177,13 +2180,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -2211,14 +2214,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="168" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2241,7 +2244,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:11">
+    <row r="4" spans="1:12">
       <c r="B4" t="s">
         <v>82</v>
       </c>
@@ -2258,42 +2261,42 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="8:8">
+    <row r="6" spans="1:12">
       <c r="H6" s="4"/>
     </row>
-    <row r="8" spans="8:11">
+    <row r="8" spans="1:12">
       <c r="H8" s="4"/>
       <c r="K8" s="4"/>
     </row>
-    <row r="9" spans="8:11">
+    <row r="9" spans="1:12">
       <c r="H9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" spans="8:11">
+    <row r="10" spans="1:12">
       <c r="H10" s="4"/>
       <c r="K10" s="4"/>
     </row>
-    <row r="11" spans="8:11">
+    <row r="11" spans="1:12">
       <c r="H11" s="4"/>
       <c r="K11" s="4"/>
     </row>
-    <row r="12" spans="8:11">
+    <row r="12" spans="1:12">
       <c r="H12" s="4"/>
       <c r="K12" s="4"/>
     </row>
-    <row r="13" spans="8:11">
+    <row r="13" spans="1:12">
       <c r="H13" s="4"/>
       <c r="K13" s="4"/>
     </row>
-    <row r="14" spans="8:11">
+    <row r="14" spans="1:12">
       <c r="H14" s="4"/>
       <c r="K14" s="4"/>
     </row>
-    <row r="15" spans="8:11">
+    <row r="15" spans="1:12">
       <c r="H15" s="4"/>
       <c r="K15" s="4"/>
     </row>
-    <row r="16" spans="8:11">
+    <row r="16" spans="1:12">
       <c r="H16" s="4"/>
       <c r="K16" s="4"/>
     </row>
@@ -2338,7 +2341,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -2362,13 +2365,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -2396,14 +2399,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="168" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2426,7 +2429,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="1:12">
       <c r="B4" t="s">
         <v>85</v>
       </c>
@@ -2440,47 +2443,47 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="8:8">
+    <row r="5" spans="1:12">
       <c r="H5" s="4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="8:8">
+    <row r="6" spans="1:12">
       <c r="H6" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="8:8">
+    <row r="7" spans="1:12">
       <c r="H7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="8:8">
+    <row r="8" spans="1:12">
       <c r="H8" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="8:8">
+    <row r="9" spans="1:12">
       <c r="H9" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="8:8">
+    <row r="10" spans="1:12">
       <c r="H10" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="11" spans="8:8">
+    <row r="11" spans="1:12">
       <c r="H11" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="8:8">
+    <row r="12" spans="1:12">
       <c r="H12" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="13" spans="8:8">
+    <row r="13" spans="1:12">
       <c r="H13" t="s">
         <v>94</v>
       </c>
@@ -2497,8 +2500,8 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="7"/>
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -2522,13 +2525,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -2556,14 +2559,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="168" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2586,7 +2589,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="1:12">
       <c r="B4" t="s">
         <v>95</v>
       </c>
@@ -2600,24 +2603,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="8:8">
+    <row r="5" spans="1:12">
       <c r="H5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="8:8">
+    <row r="6" spans="1:12">
       <c r="H6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="7" spans="8:8">
+    <row r="7" spans="1:12">
       <c r="H7" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="8:8">
+    <row r="8" spans="1:12">
       <c r="H8" t="s">
         <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="H9" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/source/Datas/__enums__.xlsx
+++ b/Configs/source/Datas/__enums__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" firstSheet="2" activeTab="6"/>
+    <workbookView windowWidth="29100" windowHeight="12700" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="101">
   <si>
     <t>##var</t>
   </si>
@@ -200,51 +200,51 @@
     <t>二郎神请神</t>
   </si>
   <si>
+    <t>拔舌鬼攻击</t>
+  </si>
+  <si>
+    <t>穷鬼吸血</t>
+  </si>
+  <si>
+    <t>铜柱鬼叠甲</t>
+  </si>
+  <si>
+    <t>铜柱鬼攻击</t>
+  </si>
+  <si>
+    <t>肉山鬼攻击</t>
+  </si>
+  <si>
+    <t>水鬼攻击</t>
+  </si>
+  <si>
+    <t>阎王攻击</t>
+  </si>
+  <si>
+    <t>阎王空过</t>
+  </si>
+  <si>
+    <t>阎王叠甲</t>
+  </si>
+  <si>
+    <t>阎王减少死期</t>
+  </si>
+  <si>
+    <t>阎王施加死期</t>
+  </si>
+  <si>
+    <t>黑白无常攻击</t>
+  </si>
+  <si>
+    <t>黑白无常打自己</t>
+  </si>
+  <si>
+    <t>黑白无常叠甲</t>
+  </si>
+  <si>
     <t>结束回合</t>
   </si>
   <si>
-    <t>拔舌鬼攻击</t>
-  </si>
-  <si>
-    <t>穷鬼吸血</t>
-  </si>
-  <si>
-    <t>铜柱鬼叠甲</t>
-  </si>
-  <si>
-    <t>铜柱鬼攻击</t>
-  </si>
-  <si>
-    <t>肉山鬼攻击</t>
-  </si>
-  <si>
-    <t>水鬼攻击</t>
-  </si>
-  <si>
-    <t>阎王攻击</t>
-  </si>
-  <si>
-    <t>阎王空过</t>
-  </si>
-  <si>
-    <t>阎王叠甲</t>
-  </si>
-  <si>
-    <t>阎王减少死期</t>
-  </si>
-  <si>
-    <t>阎王施加死期</t>
-  </si>
-  <si>
-    <t>黑白无常攻击</t>
-  </si>
-  <si>
-    <t>黑白无常打自己</t>
-  </si>
-  <si>
-    <t>黑白无常叠甲</t>
-  </si>
-  <si>
     <t>CardTypeEnum</t>
   </si>
   <si>
@@ -330,9 +330,6 @@
   </si>
   <si>
     <t>无常面具</t>
-  </si>
-  <si>
-    <t>阎罗面具</t>
   </si>
   <si>
     <t>孟婆面具</t>
@@ -1012,10 +1009,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1345,8 +1342,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:L54"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="20.875" customWidth="1"/>
@@ -1381,13 +1378,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1422,7 +1419,7 @@
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1445,7 +1442,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
         <v>19</v>
       </c>
@@ -1459,62 +1456,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="8:8">
       <c r="H5" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="8:8">
       <c r="H6" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="8:8">
       <c r="H7" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="8:8">
       <c r="H8" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="8:8">
       <c r="H9" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="8:8">
       <c r="H10" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="8:8">
       <c r="H11" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="8:8">
       <c r="H12" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="8:8">
       <c r="H13" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="8:8">
       <c r="H14" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="8:8">
       <c r="H15" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="8:8">
       <c r="H16" s="5" t="s">
         <v>32</v>
       </c>
@@ -1630,77 +1627,80 @@
       </c>
     </row>
     <row r="39" spans="8:8">
-      <c r="H39" s="6" t="s">
-        <v>55</v>
-      </c>
+      <c r="H39" s="6"/>
     </row>
     <row r="40" spans="8:8">
       <c r="H40" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="8:8">
       <c r="H41" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="42" spans="8:8">
       <c r="H42" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43" spans="8:8">
       <c r="H43" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44" spans="8:8">
       <c r="H44" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45" spans="8:8">
       <c r="H45" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="8:8">
       <c r="H46" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="8:8">
       <c r="H47" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="48" spans="8:8">
       <c r="H48" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="49" spans="8:8">
       <c r="H49" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="50" spans="8:8">
       <c r="H50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="51" spans="8:8">
       <c r="H51" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="52" spans="8:8">
       <c r="H52" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53" spans="8:8">
       <c r="H53" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="54" spans="8:8">
+      <c r="H54" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="20.875" customWidth="1"/>
@@ -1753,13 +1753,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1794,7 +1794,7 @@
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" customFormat="1" spans="1:12">
+    <row r="4" customFormat="1" spans="2:8">
       <c r="B4" t="s">
         <v>70</v>
       </c>
@@ -1828,46 +1828,46 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:12">
+    <row r="5" customFormat="1" spans="8:8">
       <c r="H5" s="5" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="1:12">
+    <row r="6" customFormat="1" spans="8:8">
       <c r="H6" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="1:12">
+    <row r="7" customFormat="1" spans="8:8">
       <c r="H7" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="8" customFormat="1" spans="1:12">
+    <row r="8" customFormat="1" spans="8:8">
       <c r="H8" s="5"/>
     </row>
-    <row r="9" customFormat="1" spans="1:12">
+    <row r="9" customFormat="1" spans="8:8">
       <c r="H9" s="5"/>
     </row>
-    <row r="10" customFormat="1" spans="1:12">
+    <row r="10" customFormat="1" spans="8:8">
       <c r="H10" s="5"/>
     </row>
-    <row r="11" customFormat="1" spans="1:12">
+    <row r="11" customFormat="1" spans="8:8">
       <c r="H11" s="5"/>
     </row>
-    <row r="12" customFormat="1" spans="1:12">
+    <row r="12" customFormat="1" spans="8:8">
       <c r="H12" s="5"/>
     </row>
-    <row r="13" customFormat="1" spans="1:12">
+    <row r="13" customFormat="1" spans="8:8">
       <c r="H13" s="5"/>
     </row>
-    <row r="14" customFormat="1" spans="1:12">
+    <row r="14" customFormat="1" spans="8:8">
       <c r="H14" s="5"/>
     </row>
-    <row r="15" customFormat="1" spans="1:12">
+    <row r="15" customFormat="1" spans="8:8">
       <c r="H15" s="5"/>
     </row>
-    <row r="16" customFormat="1" spans="1:12">
+    <row r="16" customFormat="1" spans="8:8">
       <c r="H16" s="4"/>
     </row>
     <row r="17" customFormat="1" spans="8:8">
@@ -1901,7 +1901,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -1925,13 +1925,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1959,14 +1959,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="168" spans="1:12">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="2:8">
       <c r="B4" t="s">
         <v>75</v>
       </c>
@@ -2000,15 +2000,15 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="8:8">
       <c r="H5" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="8:8">
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="8:8">
       <c r="H7" s="4"/>
     </row>
   </sheetData>
@@ -2024,7 +2024,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -2048,13 +2048,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -2082,14 +2082,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="168" spans="1:12">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="2:8">
       <c r="B4" t="s">
         <v>78</v>
       </c>
@@ -2123,17 +2123,17 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="8:8">
       <c r="H5" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="8:8">
       <c r="H6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="8:8">
       <c r="H7" t="s">
         <v>81</v>
       </c>
@@ -2151,11 +2151,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L23"/>
-  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="14.875" customWidth="1"/>
-    <col min="10" max="10" width="12.2" customWidth="1"/>
-    <col min="11" max="11" width="16.075" customWidth="1"/>
+    <col min="10" max="10" width="12.1964285714286" customWidth="1"/>
+    <col min="11" max="11" width="16.0714285714286" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -2180,13 +2180,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -2214,14 +2214,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="168" spans="1:12">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="2:11">
       <c r="B4" t="s">
         <v>82</v>
       </c>
@@ -2261,42 +2261,42 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="8:8">
       <c r="H6" s="4"/>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="8:11">
       <c r="H8" s="4"/>
       <c r="K8" s="4"/>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="8:11">
       <c r="H9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="8:11">
       <c r="H10" s="4"/>
       <c r="K10" s="4"/>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="8:11">
       <c r="H11" s="4"/>
       <c r="K11" s="4"/>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="8:11">
       <c r="H12" s="4"/>
       <c r="K12" s="4"/>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="8:11">
       <c r="H13" s="4"/>
       <c r="K13" s="4"/>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="8:11">
       <c r="H14" s="4"/>
       <c r="K14" s="4"/>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="8:11">
       <c r="H15" s="4"/>
       <c r="K15" s="4"/>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="8:11">
       <c r="H16" s="4"/>
       <c r="K16" s="4"/>
     </row>
@@ -2341,7 +2341,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -2365,13 +2365,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -2399,14 +2399,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="168" spans="1:12">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
         <v>85</v>
       </c>
@@ -2443,47 +2443,47 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="8:8">
       <c r="H5" s="4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="8:8">
       <c r="H6" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="8:8">
       <c r="H7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="8:8">
       <c r="H8" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="8:8">
       <c r="H9" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="8:8">
       <c r="H10" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="8:8">
       <c r="H11" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="8:8">
       <c r="H12" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="8:8">
       <c r="H13" t="s">
         <v>94</v>
       </c>
@@ -2500,8 +2500,8 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14"/>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="7"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -2525,13 +2525,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -2559,14 +2559,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="168" spans="1:12">
+    <row r="3" ht="219" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
         <v>95</v>
       </c>
@@ -2603,29 +2603,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="8:8">
       <c r="H5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="8:8">
       <c r="H6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="8:8">
       <c r="H7" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="8:8">
       <c r="H8" t="s">
         <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="H9" t="s">
-        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/source/Datas/__enums__.xlsx
+++ b/Configs/source/Datas/__enums__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="12700" firstSheet="2"/>
+    <workbookView windowWidth="25600" windowHeight="12080" firstSheet="2" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="102">
   <si>
     <t>##var</t>
   </si>
@@ -330,6 +330,9 @@
   </si>
   <si>
     <t>无常面具</t>
+  </si>
+  <si>
+    <t>阎罗面具</t>
   </si>
   <si>
     <t>孟婆面具</t>
@@ -1009,10 +1012,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1342,8 +1345,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L54"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:L53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="20.875" customWidth="1"/>
@@ -1378,13 +1381,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1419,7 +1422,7 @@
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1442,7 +1445,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="1:12">
       <c r="B4" t="s">
         <v>19</v>
       </c>
@@ -1456,62 +1459,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="8:8">
+    <row r="5" spans="1:12">
       <c r="H5" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="8:8">
+    <row r="6" spans="1:12">
       <c r="H6" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="8:8">
+    <row r="7" spans="1:12">
       <c r="H7" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="8:8">
+    <row r="8" spans="1:12">
       <c r="H8" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="8:8">
+    <row r="9" spans="1:12">
       <c r="H9" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="8:8">
+    <row r="10" spans="1:12">
       <c r="H10" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="8:8">
+    <row r="11" spans="1:12">
       <c r="H11" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="8:8">
+    <row r="12" spans="1:12">
       <c r="H12" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="8:8">
+    <row r="13" spans="1:12">
       <c r="H13" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="8:8">
+    <row r="14" spans="1:12">
       <c r="H14" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="8:8">
+    <row r="15" spans="1:12">
       <c r="H15" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="8:8">
+    <row r="16" spans="1:12">
       <c r="H16" s="5" t="s">
         <v>32</v>
       </c>
@@ -1627,80 +1630,77 @@
       </c>
     </row>
     <row r="39" spans="8:8">
-      <c r="H39" s="6"/>
+      <c r="H39" s="6" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="40" spans="8:8">
       <c r="H40" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="41" spans="8:8">
       <c r="H41" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42" spans="8:8">
       <c r="H42" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="43" spans="8:8">
       <c r="H43" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44" spans="8:8">
       <c r="H44" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="8:8">
       <c r="H45" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="46" spans="8:8">
       <c r="H46" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="47" spans="8:8">
       <c r="H47" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="48" spans="8:8">
       <c r="H48" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="49" spans="8:8">
-      <c r="H49" s="6" t="s">
-        <v>64</v>
+      <c r="H49" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="50" spans="8:8">
-      <c r="H50" t="s">
-        <v>65</v>
+      <c r="H50" s="6" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="8:8">
       <c r="H51" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52" spans="8:8">
       <c r="H52" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53" spans="8:8">
-      <c r="H53" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="54" spans="8:8">
-      <c r="H54" t="s">
+      <c r="H53" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="20.875" customWidth="1"/>
@@ -1753,13 +1753,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1794,7 +1794,7 @@
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" customFormat="1" spans="2:8">
+    <row r="4" customFormat="1" spans="1:12">
       <c r="B4" t="s">
         <v>70</v>
       </c>
@@ -1828,46 +1828,46 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="8:8">
+    <row r="5" customFormat="1" spans="1:12">
       <c r="H5" s="5" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="8:8">
+    <row r="6" customFormat="1" spans="1:12">
       <c r="H6" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="8:8">
+    <row r="7" customFormat="1" spans="1:12">
       <c r="H7" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="8" customFormat="1" spans="8:8">
+    <row r="8" customFormat="1" spans="1:12">
       <c r="H8" s="5"/>
     </row>
-    <row r="9" customFormat="1" spans="8:8">
+    <row r="9" customFormat="1" spans="1:12">
       <c r="H9" s="5"/>
     </row>
-    <row r="10" customFormat="1" spans="8:8">
+    <row r="10" customFormat="1" spans="1:12">
       <c r="H10" s="5"/>
     </row>
-    <row r="11" customFormat="1" spans="8:8">
+    <row r="11" customFormat="1" spans="1:12">
       <c r="H11" s="5"/>
     </row>
-    <row r="12" customFormat="1" spans="8:8">
+    <row r="12" customFormat="1" spans="1:12">
       <c r="H12" s="5"/>
     </row>
-    <row r="13" customFormat="1" spans="8:8">
+    <row r="13" customFormat="1" spans="1:12">
       <c r="H13" s="5"/>
     </row>
-    <row r="14" customFormat="1" spans="8:8">
+    <row r="14" customFormat="1" spans="1:12">
       <c r="H14" s="5"/>
     </row>
-    <row r="15" customFormat="1" spans="8:8">
+    <row r="15" customFormat="1" spans="1:12">
       <c r="H15" s="5"/>
     </row>
-    <row r="16" customFormat="1" spans="8:8">
+    <row r="16" customFormat="1" spans="1:12">
       <c r="H16" s="4"/>
     </row>
     <row r="17" customFormat="1" spans="8:8">
@@ -1901,7 +1901,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14" outlineLevelRow="6"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -1925,13 +1925,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -1959,14 +1959,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="168" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="1:12">
       <c r="B4" t="s">
         <v>75</v>
       </c>
@@ -2000,15 +2000,15 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="8:8">
+    <row r="5" spans="1:12">
       <c r="H5" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="8:8">
+    <row r="6" spans="1:12">
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="8:8">
+    <row r="7" spans="1:12">
       <c r="H7" s="4"/>
     </row>
   </sheetData>
@@ -2024,7 +2024,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14" outlineLevelRow="6"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -2048,13 +2048,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -2082,14 +2082,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="168" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="1:12">
       <c r="B4" t="s">
         <v>78</v>
       </c>
@@ -2123,17 +2123,17 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="8:8">
+    <row r="5" spans="1:12">
       <c r="H5" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="8:8">
+    <row r="6" spans="1:12">
       <c r="H6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="8:8">
+    <row r="7" spans="1:12">
       <c r="H7" t="s">
         <v>81</v>
       </c>
@@ -2151,11 +2151,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L23"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="14.875" customWidth="1"/>
-    <col min="10" max="10" width="12.1964285714286" customWidth="1"/>
-    <col min="11" max="11" width="16.0714285714286" customWidth="1"/>
+    <col min="10" max="10" width="12.2" customWidth="1"/>
+    <col min="11" max="11" width="16.075" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -2180,13 +2180,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -2214,14 +2214,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="168" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:11">
+    <row r="4" spans="1:12">
       <c r="B4" t="s">
         <v>82</v>
       </c>
@@ -2261,42 +2261,42 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="8:8">
+    <row r="6" spans="1:12">
       <c r="H6" s="4"/>
     </row>
-    <row r="8" spans="8:11">
+    <row r="8" spans="1:12">
       <c r="H8" s="4"/>
       <c r="K8" s="4"/>
     </row>
-    <row r="9" spans="8:11">
+    <row r="9" spans="1:12">
       <c r="H9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" spans="8:11">
+    <row r="10" spans="1:12">
       <c r="H10" s="4"/>
       <c r="K10" s="4"/>
     </row>
-    <row r="11" spans="8:11">
+    <row r="11" spans="1:12">
       <c r="H11" s="4"/>
       <c r="K11" s="4"/>
     </row>
-    <row r="12" spans="8:11">
+    <row r="12" spans="1:12">
       <c r="H12" s="4"/>
       <c r="K12" s="4"/>
     </row>
-    <row r="13" spans="8:11">
+    <row r="13" spans="1:12">
       <c r="H13" s="4"/>
       <c r="K13" s="4"/>
     </row>
-    <row r="14" spans="8:11">
+    <row r="14" spans="1:12">
       <c r="H14" s="4"/>
       <c r="K14" s="4"/>
     </row>
-    <row r="15" spans="8:11">
+    <row r="15" spans="1:12">
       <c r="H15" s="4"/>
       <c r="K15" s="4"/>
     </row>
-    <row r="16" spans="8:11">
+    <row r="16" spans="1:12">
       <c r="H16" s="4"/>
       <c r="K16" s="4"/>
     </row>
@@ -2341,7 +2341,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -2365,13 +2365,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -2399,14 +2399,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="168" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="1:12">
       <c r="B4" t="s">
         <v>85</v>
       </c>
@@ -2443,47 +2443,47 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="8:8">
+    <row r="5" spans="1:12">
       <c r="H5" s="4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="8:8">
+    <row r="6" spans="1:12">
       <c r="H6" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="8:8">
+    <row r="7" spans="1:12">
       <c r="H7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="8:8">
+    <row r="8" spans="1:12">
       <c r="H8" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="8:8">
+    <row r="9" spans="1:12">
       <c r="H9" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="8:8">
+    <row r="10" spans="1:12">
       <c r="H10" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="11" spans="8:8">
+    <row r="11" spans="1:12">
       <c r="H11" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="8:8">
+    <row r="12" spans="1:12">
       <c r="H12" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="13" spans="8:8">
+    <row r="13" spans="1:12">
       <c r="H13" t="s">
         <v>94</v>
       </c>
@@ -2500,8 +2500,8 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelRow="7"/>
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -2525,13 +2525,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -2559,14 +2559,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="219" spans="1:12">
+    <row r="3" ht="168" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="1:12">
       <c r="B4" t="s">
         <v>95</v>
       </c>
@@ -2603,24 +2603,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="8:8">
+    <row r="5" spans="1:12">
       <c r="H5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="8:8">
+    <row r="6" spans="1:12">
       <c r="H6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="7" spans="8:8">
+    <row r="7" spans="1:12">
       <c r="H7" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="8:8">
+    <row r="8" spans="1:12">
       <c r="H8" t="s">
         <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="H9" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/source/Datas/__enums__.xlsx
+++ b/Configs/source/Datas/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" firstSheet="2" activeTab="6"/>
+    <workbookView windowWidth="25600" windowHeight="12080" firstSheet="2" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
@@ -14,6 +14,7 @@
     <sheet name="GameMap" sheetId="3" r:id="rId5"/>
     <sheet name="GameLevel" sheetId="6" r:id="rId6"/>
     <sheet name="Mask" sheetId="8" r:id="rId7"/>
+    <sheet name="Buff" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="105">
   <si>
     <t>##var</t>
   </si>
@@ -339,6 +340,15 @@
   </si>
   <si>
     <t>二郎神面具</t>
+  </si>
+  <si>
+    <t>BuffEnum</t>
+  </si>
+  <si>
+    <t>碎魂效果</t>
+  </si>
+  <si>
+    <t>壮魂效果</t>
   </si>
 </sst>
 </file>
@@ -2635,4 +2645,129 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14" outlineLevelRow="5"/>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" ht="168" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="B4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="H5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="H6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Configs/source/Datas/__enums__.xlsx
+++ b/Configs/source/Datas/__enums__.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="106">
   <si>
     <t>##var</t>
   </si>
@@ -349,6 +349,9 @@
   </si>
   <si>
     <t>壮魂效果</t>
+  </si>
+  <si>
+    <t>返回本我效果</t>
   </si>
 </sst>
 </file>
@@ -2650,8 +2653,8 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14" outlineLevelRow="5"/>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14" outlineLevelRow="6"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -2763,6 +2766,11 @@
         <v>104</v>
       </c>
     </row>
+    <row r="7" spans="1:12">
+      <c r="H7" t="s">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Configs/source/Datas/__enums__.xlsx
+++ b/Configs/source/Datas/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" firstSheet="2" activeTab="7"/>
+    <workbookView windowWidth="25600" windowHeight="12080" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="149">
   <si>
     <t>##var</t>
   </si>
@@ -246,6 +246,99 @@
     <t>结束回合</t>
   </si>
   <si>
+    <t>孟婆汤_攻击一</t>
+  </si>
+  <si>
+    <t>孟婆汤_攻击二</t>
+  </si>
+  <si>
+    <t>孟婆汤_攻击三</t>
+  </si>
+  <si>
+    <t>孟婆汤_功能一</t>
+  </si>
+  <si>
+    <t>孟婆汤_功能二</t>
+  </si>
+  <si>
+    <t>孟婆汤_功能三</t>
+  </si>
+  <si>
+    <t>孟婆汤_请神</t>
+  </si>
+  <si>
+    <t>孟婆汤_AF平衡药水_1</t>
+  </si>
+  <si>
+    <t>孟婆汤_AF功能药水_12</t>
+  </si>
+  <si>
+    <t>孟婆汤_AF功能药水_13</t>
+  </si>
+  <si>
+    <t>孟婆汤_三混平衡药水_1</t>
+  </si>
+  <si>
+    <t>孟婆汤_三混功能药水_121</t>
+  </si>
+  <si>
+    <t>孟婆汤_三混功能药水_131</t>
+  </si>
+  <si>
+    <t>孟婆汤_AF攻击药水_21</t>
+  </si>
+  <si>
+    <t>孟婆汤_AF平衡药水_2</t>
+  </si>
+  <si>
+    <t>孟婆汤_AF功能药水_23</t>
+  </si>
+  <si>
+    <t>孟婆汤_三混攻击药水_211</t>
+  </si>
+  <si>
+    <t>孟婆汤_三混平衡药水_2</t>
+  </si>
+  <si>
+    <t>孟婆汤_三混攻击药水_231</t>
+  </si>
+  <si>
+    <t>孟婆汤_AF攻击药水_31</t>
+  </si>
+  <si>
+    <t>孟婆汤_AF攻击药水_32</t>
+  </si>
+  <si>
+    <t>孟婆汤_AF平衡药水_3</t>
+  </si>
+  <si>
+    <t>孟婆汤_三混攻击药水_311</t>
+  </si>
+  <si>
+    <t>孟婆汤_三混攻击药水_321</t>
+  </si>
+  <si>
+    <t>孟婆汤_三混平衡药水_3</t>
+  </si>
+  <si>
+    <t>孟婆汤_AI平衡药水_1</t>
+  </si>
+  <si>
+    <t>孟婆汤_AI攻击药水_21</t>
+  </si>
+  <si>
+    <t>孟婆汤_AI攻击药水_31</t>
+  </si>
+  <si>
+    <t>孟婆汤_FI平衡药水_1</t>
+  </si>
+  <si>
+    <t>孟婆汤_FI功能药水_21</t>
+  </si>
+  <si>
+    <t>孟婆汤_FI功能药水_31</t>
+  </si>
+  <si>
     <t>CardTypeEnum</t>
   </si>
   <si>
@@ -352,6 +445,42 @@
   </si>
   <si>
     <t>返回本我效果</t>
+  </si>
+  <si>
+    <t>死期</t>
+  </si>
+  <si>
+    <t>死期到0时，生命减少为0</t>
+  </si>
+  <si>
+    <t>黑无常</t>
+  </si>
+  <si>
+    <t>造成伤害无视敌方护甲</t>
+  </si>
+  <si>
+    <t>白无常</t>
+  </si>
+  <si>
+    <t>造成的伤害改为回血，回血改为造成伤害（仅一次防止无限循环）</t>
+  </si>
+  <si>
+    <t>禁武令</t>
+  </si>
+  <si>
+    <t>造成伤害后自己也掉血</t>
+  </si>
+  <si>
+    <t>卸甲令</t>
+  </si>
+  <si>
+    <t>护甲清零，不能获得护甲</t>
+  </si>
+  <si>
+    <t>监禁令</t>
+  </si>
+  <si>
+    <t>不能行动（但列表会往下走）</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +1146,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1037,6 +1166,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1358,7 +1490,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:L84"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -1715,6 +1847,161 @@
     <row r="53" spans="8:8">
       <c r="H53" t="s">
         <v>69</v>
+      </c>
+    </row>
+    <row r="54" spans="8:8">
+      <c r="H54" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="55" spans="8:8">
+      <c r="H55" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="56" spans="8:8">
+      <c r="H56" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="57" spans="8:8">
+      <c r="H57" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="58" spans="8:8">
+      <c r="H58" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="59" spans="8:8">
+      <c r="H59" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="60" spans="8:8">
+      <c r="H60" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="61" spans="8:8">
+      <c r="H61" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="62" spans="8:8">
+      <c r="H62" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="63" spans="8:8">
+      <c r="H63" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="64" spans="8:8">
+      <c r="H64" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="65" spans="8:8">
+      <c r="H65" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="66" spans="8:8">
+      <c r="H66" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67" spans="8:8">
+      <c r="H67" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="68" spans="8:8">
+      <c r="H68" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="69" spans="8:8">
+      <c r="H69" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="70" spans="8:8">
+      <c r="H70" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="71" spans="8:8">
+      <c r="H71" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="72" spans="8:8">
+      <c r="H72" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="73" spans="8:8">
+      <c r="H73" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="74" spans="8:8">
+      <c r="H74" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="75" spans="8:8">
+      <c r="H75" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="76" spans="8:8">
+      <c r="H76" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="77" spans="8:8">
+      <c r="H77" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="78" spans="8:8">
+      <c r="H78" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="79" spans="8:8">
+      <c r="H79" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="80" spans="8:8">
+      <c r="H80" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="81" spans="8:8">
+      <c r="H81" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="82" spans="8:8">
+      <c r="H82" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="83" spans="8:8">
+      <c r="H83" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="84" spans="8:8">
+      <c r="H84" s="7" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1832,28 +2119,28 @@
     </row>
     <row r="4" customFormat="1" spans="1:12">
       <c r="B4" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:12">
       <c r="H5" s="5" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" customFormat="1" spans="1:12">
       <c r="H6" s="5" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:12">
       <c r="H7" s="5" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:12">
@@ -2004,18 +2291,18 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="H5" s="4" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2127,28 +2414,28 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="H5" s="4" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="H6" t="s">
-        <v>80</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="H7" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -2259,19 +2546,19 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="J4">
         <v>-1</v>
       </c>
       <c r="K4" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2444,7 +2731,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -2458,47 +2745,47 @@
     </row>
     <row r="5" spans="1:12">
       <c r="H5" s="4" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="H6" t="s">
-        <v>87</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="H7" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="H8" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="H9" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="H10" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="H11" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="H12" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="H13" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -2604,13 +2891,13 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2618,27 +2905,27 @@
     </row>
     <row r="5" spans="1:12">
       <c r="H5" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="H6" t="s">
-        <v>98</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="H7" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="H8" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="H9" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -2653,8 +2940,8 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14" outlineLevelRow="6"/>
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -2744,7 +3031,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -2758,17 +3045,65 @@
     </row>
     <row r="5" spans="1:12">
       <c r="H5" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="H6" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="H7" t="s">
-        <v>105</v>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="H8" t="s">
+        <v>137</v>
+      </c>
+      <c r="K8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="H9" t="s">
+        <v>139</v>
+      </c>
+      <c r="K9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="H10" t="s">
+        <v>141</v>
+      </c>
+      <c r="K10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="H11" t="s">
+        <v>143</v>
+      </c>
+      <c r="K11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="H12" t="s">
+        <v>145</v>
+      </c>
+      <c r="K12" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="H13" t="s">
+        <v>147</v>
+      </c>
+      <c r="K13" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/source/Datas/__enums__.xlsx
+++ b/Configs/source/Datas/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" firstSheet="2"/>
+    <workbookView windowWidth="25600" windowHeight="12080" firstSheet="2" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
@@ -462,7 +462,7 @@
     <t>白无常</t>
   </si>
   <si>
-    <t>造成的伤害改为回血，回血改为造成伤害（仅一次防止无限循环）</t>
+    <t>造成伤害恢复等量生命</t>
   </si>
   <si>
     <t>禁武令</t>

--- a/Configs/source/Datas/__enums__.xlsx
+++ b/Configs/source/Datas/__enums__.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="151">
   <si>
     <t>##var</t>
   </si>
@@ -481,6 +481,12 @@
   </si>
   <si>
     <t>不能行动（但列表会往下走）</t>
+  </si>
+  <si>
+    <t>二郎神</t>
+  </si>
+  <si>
+    <t>使用对面的行动对对手造成影响（类似死期这种不处理）</t>
   </si>
 </sst>
 </file>
@@ -2940,7 +2946,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -3106,6 +3112,14 @@
         <v>148</v>
       </c>
     </row>
+    <row r="14" spans="1:12">
+      <c r="H14" t="s">
+        <v>149</v>
+      </c>
+      <c r="K14" t="s">
+        <v>150</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Configs/source/Datas/__enums__.xlsx
+++ b/Configs/source/Datas/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" firstSheet="2" activeTab="7"/>
+    <workbookView windowWidth="25600" windowHeight="12080" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="156">
   <si>
     <t>##var</t>
   </si>
@@ -361,6 +361,21 @@
   </si>
   <si>
     <t>拔舌鬼</t>
+  </si>
+  <si>
+    <t>穷鬼</t>
+  </si>
+  <si>
+    <t>铜柱鬼</t>
+  </si>
+  <si>
+    <t>肉山鬼</t>
+  </si>
+  <si>
+    <t>阎王</t>
+  </si>
+  <si>
+    <t>黑白无常</t>
   </si>
   <si>
     <t>IntentEnum</t>
@@ -2206,8 +2221,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14" outlineLevelRow="6"/>
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -2312,10 +2327,29 @@
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="H6" s="4"/>
+      <c r="H6" s="4" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="H7" s="4"/>
+      <c r="H7" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="H8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="H9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="H10" t="s">
+        <v>113</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2420,7 +2454,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -2431,17 +2465,17 @@
     </row>
     <row r="5" spans="1:12">
       <c r="H5" s="4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="H6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="H7" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -2552,19 +2586,19 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="J4">
         <v>-1</v>
       </c>
       <c r="K4" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2737,7 +2771,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -2751,47 +2785,47 @@
     </row>
     <row r="5" spans="1:12">
       <c r="H5" s="4" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="H6" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="H7" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="H8" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="H9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="H10" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="H11" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="H12" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="H13" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2897,13 +2931,13 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2911,27 +2945,27 @@
     </row>
     <row r="5" spans="1:12">
       <c r="H5" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="H6" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="H7" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="H8" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="H9" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -3037,7 +3071,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -3051,73 +3085,73 @@
     </row>
     <row r="5" spans="1:12">
       <c r="H5" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="H6" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="H7" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="H8" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="K8" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="H9" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="K9" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="H10" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="K10" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="H11" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="K11" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="H12" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="K12" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="H13" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="K13" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="H14" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="K14" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
